--- a/a_materials/Tentative Schedule.xlsx
+++ b/a_materials/Tentative Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98D5DA9-B3D1-5F44-98DC-BD829DE3E439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129FD4A3-DE6E-0D4B-B1E4-01C5B50448CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Introduction</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Final Project Presentations</t>
   </si>
   <si>
-    <t>Sampling/Confidence Intervals and Hypothesis Testing</t>
-  </si>
-  <si>
     <t>Topic</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
   </si>
   <si>
     <t>NO CLASS (Election Day)</t>
-  </si>
-  <si>
-    <t>Multiple Linear Regression (V)</t>
   </si>
   <si>
     <t>Guest Lecture</t>
@@ -503,10 +497,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -539,7 +533,7 @@
         <v>46266</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -557,7 +551,7 @@
         <v>46273</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -565,9 +559,7 @@
         <f t="shared" si="0"/>
         <v>46275</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
@@ -593,7 +585,7 @@
         <v>46287</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -611,7 +603,7 @@
         <v>46294</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -656,7 +648,7 @@
         <v>46310</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -674,7 +666,7 @@
         <v>46317</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -683,7 +675,7 @@
         <v>46322</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -701,7 +693,7 @@
         <v>46329</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -710,7 +702,7 @@
         <v>46331</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">

--- a/a_materials/Tentative Schedule.xlsx
+++ b/a_materials/Tentative Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/IntroEconometrics/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129FD4A3-DE6E-0D4B-B1E4-01C5B50448CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3269BB6A-308E-8945-ABBD-53BEB26DBA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
+    <workbookView xWindow="-31220" yWindow="1300" windowWidth="27040" windowHeight="19220" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>Introduction</t>
   </si>
@@ -94,7 +94,7 @@
     <t>Guest Lecture</t>
   </si>
   <si>
-    <t>Difference-in-Differences (V)</t>
+    <t>Difference-in-Differences</t>
   </si>
 </sst>
 </file>
@@ -191,9 +191,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -231,7 +231,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -337,7 +337,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -479,7 +479,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -594,7 +594,7 @@
         <v>46289</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -612,7 +612,7 @@
         <v>46296</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -630,7 +630,7 @@
         <v>46303</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -657,7 +657,7 @@
         <v>46315</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -665,16 +665,14 @@
         <f t="shared" si="0"/>
         <v>46317</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="B20" s="4"/>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
         <v>46322</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -684,7 +682,7 @@
         <v>46324</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">

--- a/a_materials/Tentative Schedule.xlsx
+++ b/a_materials/Tentative Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/IntroEconometrics/a_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3269BB6A-308E-8945-ABBD-53BEB26DBA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A52325F-4855-E94F-AB0D-0FE15C24F36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31220" yWindow="1300" windowWidth="27040" windowHeight="19220" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>Introduction</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>Difference-in-Differences</t>
+  </si>
+  <si>
+    <t>Review</t>
   </si>
 </sst>
 </file>
@@ -191,9 +194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -231,7 +234,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -337,7 +340,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -479,7 +482,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -621,7 +624,7 @@
         <v>46301</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -629,8 +632,8 @@
         <f t="shared" si="0"/>
         <v>46303</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>9</v>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">

--- a/a_materials/Tentative Schedule.xlsx
+++ b/a_materials/Tentative Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A52325F-4855-E94F-AB0D-0FE15C24F36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F26989-5E9B-EB42-AABB-56BDE8DD09F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>Introduction</t>
   </si>
@@ -97,7 +97,10 @@
     <t>Difference-in-Differences</t>
   </si>
   <si>
-    <t>Review</t>
+    <t>Office Hours</t>
+  </si>
+  <si>
+    <t>Panel Data/ Review</t>
   </si>
 </sst>
 </file>
@@ -633,7 +636,7 @@
         <v>46303</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -668,7 +671,9 @@
         <f t="shared" si="0"/>
         <v>46317</v>
       </c>
-      <c r="B20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
